--- a/python/Kalkulator_Produksi_Sesuai_Excel_update.xlsx
+++ b/python/Kalkulator_Produksi_Sesuai_Excel_update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\skripsi_forecasting\python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{289DBDDD-6FE0-46EA-8AD4-68E46E46ED64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB99351-E4C5-4A32-B8D7-BA5DFE7960EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Format Per Produk" sheetId="1" r:id="rId1"/>
@@ -28,28 +28,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1127,9 +1105,9 @@
       <c r="B24" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="C24" s="4" t="e" cm="1">
-        <f t="array" ref="C24">B20*B19B3330&amp;" ml"</f>
-        <v>#NAME?</v>
+      <c r="C24" s="4" t="str">
+        <f>B20*30&amp;" ml"</f>
+        <v>750 ml</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>11</v>
